--- a/NuevaData/Presentacion/Investigacion/FACTOR 3. PROFESORES/a. Informes de participación de los docentes/F3_Participacion_Docente_Capacitacion.xlsx
+++ b/NuevaData/Presentacion/Investigacion/FACTOR 3. PROFESORES/a. Informes de participación de los docentes/F3_Participacion_Docente_Capacitacion.xlsx
@@ -9,11 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitación docente" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movilidad" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificados" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movilidad" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Capacitación docente'!$A$4:$J$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Movilidad'!$A$4:$I$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Capacitación docente'!$A$4:$J$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Certificados'!$A$4:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Movilidad'!$A$4:$I$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -599,10 +601,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Participación de los profesores de la Maestría en capacitación académica y administrativa, y movilidad académica. Información en actualización: se solicitó a los profesores reportar con soporte las capacitaciones adicionales del periodo 2025-2026 (columna J de la hoja «Capacitación docente»).</t>
+          <t>Participación de los profesores de la Maestría en capacitación académica y administrativa, y movilidad académica. Incluye las capacitaciones adicionales con certificado reportadas por los profesores (columna J de la hoja «Capacitación docente» y hoja «Certificados»).</t>
         </is>
       </c>
     </row>
@@ -691,14 +693,14 @@
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>43 %</t>
+          <t>48 %</t>
         </is>
       </c>
       <c r="G10" s="9" t="n">
@@ -743,7 +745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -755,7 +757,7 @@
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -820,7 +822,7 @@
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>Capacitaciones 2025-2026 reportadas por el profesor (por diligenciar)</t>
+          <t>Otras capacitaciones con certificado</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1256,11 @@
           <t>Asociado</t>
         </is>
       </c>
-      <c r="J20" s="12" t="n"/>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>Taller de formación EUR-ACE «Aseguramiento de calidad y acreditación internacional EUR-ACE de programas educativos en ingeniería» — ENAEE, ENTEA y LACCEI (Girardot, Colombia) (08/11/2022 al 10/11/2022)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
@@ -1394,7 +1400,12 @@
           <t>Asociado</t>
         </is>
       </c>
-      <c r="J25" s="6" t="n"/>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Introduction to GeoWebApp Building with open-source tools (curso en línea) — Universidad de Twente (ITC) y Geoversity (13/05/2024, 40 h)
+Curso Internacional de Competencias Docentes y Diseño de Materiales Didácticos para la Educación en Línea (título propio, calificación 9,60) — Universidad Internacional de La Rioja (UNIR) (04/05/2026 al 05/07/2026, 125 h)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
@@ -1458,7 +1469,11 @@
       </c>
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="n"/>
-      <c r="J27" s="6" t="n"/>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Data Science and Machine Learning: Making Data-Driven Decisions — MIT Schwarzman College of Computing y MIT IDSS (agosto de 2023)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="n">
@@ -1628,30 +1643,54 @@
       </c>
       <c r="B34" s="12" t="inlineStr">
         <is>
-          <t>Vera Parra Nelson Enrique</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
+          <t>Vanegas Ayala Sebastian Camilo</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n"/>
       <c r="D34" s="12" t="n"/>
       <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>Curso y aprobo especializado I y II 2023-1</t>
-        </is>
-      </c>
-      <c r="G34" s="12" t="n">
-        <v>2023</v>
-      </c>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
       <c r="H34" s="12" t="n"/>
       <c r="I34" s="12" t="n"/>
-      <c r="J34" s="12" t="n"/>
+      <c r="J34" s="12" t="inlineStr">
+        <is>
+          <t>Taller «Instalación local de modelos de IA» — Vicerrectoría Académica y Comité PlanEsTIC-UD (16/07/2025, 1 h)
+Taller «Automatización de tareas de ofimática con IA a través del uso de protocolo MCP» — Vicerrectoría Académica y Comité PlanEsTIC-UD (15/07/2025, 1 h)
+Taller «Da vida a tus ideas con presentaciones creativas e impactantes en Gamma AI» — Vicerrectoría Académica y Comité PlanEsTIC-UD (20/08/2025, 1 h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Vera Parra Nelson Enrique</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>Curso y aprobo especializado I y II 2023-1</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="6" t="n"/>
+      <c r="J35" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J34"/>
+  <autoFilter ref="A4:J35"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
@@ -1661,6 +1700,320 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Capacitaciones con certificado reportadas por los profesores</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Certificados recientes entregados por los profesores; los documentos se resguardan en el archivo del programa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Profesor</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Capacitación</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Entidad</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Soporte</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Gomez Vargas Ernesto</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Taller de formación EUR-ACE «Aseguramiento de calidad y acreditación internacional EUR-ACE de programas educativos en ingeniería»</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>ENAEE, ENTEA y LACCEI (Girardot, Colombia)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>08/11/2022 al 10/11/2022</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Certificado en archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Ortiz Davila Alvaro Enrique</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Introduction to GeoWebApp Building with open-source tools (curso en línea)</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Universidad de Twente (ITC) y Geoversity</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>13/05/2024</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Certificado en archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Ortiz Davila Alvaro Enrique</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Curso Internacional de Competencias Docentes y Diseño de Materiales Didácticos para la Educación en Línea (título propio, calificación 9,60)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Universidad Internacional de La Rioja (UNIR)</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>04/05/2026 al 05/07/2026</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2026</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Certificado en archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Plazas Nossa Leonardo</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Data Science and Machine Learning: Making Data-Driven Decisions</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>MIT Schwarzman College of Computing y MIT IDSS</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>agosto de 2023</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>2023</v>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Certificado en archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Vanegas Ayala Sebastian Camilo</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Taller «Instalación local de modelos de IA»</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Vicerrectoría Académica y Comité PlanEsTIC-UD</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>16/07/2025</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Certificado en archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Vanegas Ayala Sebastian Camilo</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Taller «Automatización de tareas de ofimática con IA a través del uso de protocolo MCP»</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Vicerrectoría Académica y Comité PlanEsTIC-UD</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>15/07/2025</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Certificado en archivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Vanegas Ayala Sebastian Camilo</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Taller «Da vida a tus ideas con presentaciones creativas e impactantes en Gamma AI»</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Vicerrectoría Académica y Comité PlanEsTIC-UD</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>20/08/2025</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Certificado en archivo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G11"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/NuevaData/Presentacion/Investigacion/FACTOR 3. PROFESORES/a. Informes de participación de los docentes/F3_Participacion_Docente_Capacitacion.xlsx
+++ b/NuevaData/Presentacion/Investigacion/FACTOR 3. PROFESORES/a. Informes de participación de los docentes/F3_Participacion_Docente_Capacitacion.xlsx
@@ -9,13 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitación docente" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Certificados" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movilidad" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movilidad" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Capacitación docente'!$A$4:$J$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Certificados'!$A$4:$G$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Movilidad'!$A$4:$I$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Capacitación docente'!$A$4:$K$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Movilidad'!$A$4:$I$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +78,12 @@
       <i val="1"/>
       <color rgb="004B5563"/>
       <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001F5FA8"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="6">
@@ -180,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,6 +212,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -601,10 +611,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="45" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Participación de los profesores de la Maestría en capacitación académica y administrativa, y movilidad académica. Incluye las capacitaciones adicionales con certificado reportadas por los profesores (columna J de la hoja «Capacitación docente» y hoja «Certificados»).</t>
+          <t>Participación de los profesores de la Maestría en capacitación académica y administrativa, y movilidad académica. Incluye las capacitaciones adicionales con certificado reportadas por los profesores (columna J de la hoja «Capacitación docente»); los certificados se adjuntan como soporte en la carpeta «Anexos/Certificados» (columna K).</t>
         </is>
       </c>
     </row>
@@ -745,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -758,6 +768,7 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="70" customWidth="1" min="10" max="10"/>
+    <col width="44" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -823,6 +834,11 @@
       <c r="J4" s="11" t="inlineStr">
         <is>
           <t>Otras capacitaciones con certificado</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>Soporte (certificados en Anexos)</t>
         </is>
       </c>
     </row>
@@ -855,6 +871,7 @@
         </is>
       </c>
       <c r="J5" s="6" t="n"/>
+      <c r="K5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="n">
@@ -883,6 +900,7 @@
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
@@ -905,6 +923,7 @@
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="n">
@@ -927,6 +946,7 @@
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -949,6 +969,7 @@
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="6" t="n"/>
       <c r="J9" s="6" t="n"/>
+      <c r="K9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="n">
@@ -977,6 +998,7 @@
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -1007,6 +1029,7 @@
         </is>
       </c>
       <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="n">
@@ -1035,6 +1058,7 @@
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
@@ -1057,6 +1081,7 @@
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="6" t="n"/>
+      <c r="K13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="n">
@@ -1079,6 +1104,7 @@
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n">
@@ -1115,6 +1141,7 @@
         </is>
       </c>
       <c r="J15" s="6" t="n"/>
+      <c r="K15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n">
@@ -1137,6 +1164,7 @@
       <c r="H16" s="12" t="n"/>
       <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -1165,6 +1193,7 @@
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="n"/>
       <c r="J17" s="6" t="n"/>
+      <c r="K17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n">
@@ -1193,6 +1222,7 @@
       <c r="H18" s="12" t="n"/>
       <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n">
@@ -1221,6 +1251,7 @@
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="6" t="n"/>
+      <c r="K19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n">
@@ -1259,6 +1290,11 @@
       <c r="J20" s="12" t="inlineStr">
         <is>
           <t>Taller de formación EUR-ACE «Aseguramiento de calidad y acreditación internacional EUR-ACE de programas educativos en ingeniería» — ENAEE, ENTEA y LACCEI (Girardot, Colombia) (08/11/2022 al 10/11/2022)</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>Ernesto Gómez Vargas.pdf</t>
         </is>
       </c>
     </row>
@@ -1291,6 +1327,7 @@
         </is>
       </c>
       <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n">
@@ -1321,6 +1358,7 @@
         </is>
       </c>
       <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -1343,6 +1381,7 @@
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="6" t="n"/>
       <c r="J23" s="6" t="n"/>
+      <c r="K23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="n">
@@ -1371,6 +1410,7 @@
       <c r="H24" s="12" t="n"/>
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
@@ -1406,6 +1446,12 @@
 Curso Internacional de Competencias Docentes y Diseño de Materiales Didácticos para la Educación en Línea (título propio, calificación 9,60) — Universidad Internacional de La Rioja (UNIR) (04/05/2026 al 05/07/2026, 125 h)</t>
         </is>
       </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>Alvaro Ortiz - 2024 - Introduction to GeoWebApp Building with open-source tools.pdf
+Alvaro Ortiz - 2026 - Competencias docentes y materiales didacticos para educacion en linea.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="n">
@@ -1442,6 +1488,7 @@
         </is>
       </c>
       <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
@@ -1472,6 +1519,11 @@
       <c r="J27" s="6" t="inlineStr">
         <is>
           <t>Data Science and Machine Learning: Making Data-Driven Decisions — MIT Schwarzman College of Computing y MIT IDSS (agosto de 2023)</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>LEONARDO PLAZAS NOSSA - certificate-2023.pdf</t>
         </is>
       </c>
     </row>
@@ -1496,6 +1548,7 @@
       <c r="H28" s="12" t="n"/>
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
@@ -1518,6 +1571,7 @@
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="n"/>
       <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="12" t="n">
@@ -1554,6 +1608,7 @@
         </is>
       </c>
       <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -1576,6 +1631,7 @@
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="n"/>
       <c r="J31" s="6" t="n"/>
+      <c r="K31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="12" t="n">
@@ -1606,6 +1662,7 @@
         </is>
       </c>
       <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
@@ -1636,6 +1693,7 @@
         </is>
       </c>
       <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="12" t="n">
@@ -1660,6 +1718,11 @@
 Taller «Da vida a tus ideas con presentaciones creativas e impactantes en Gamma AI» — Vicerrectoría Académica y Comité PlanEsTIC-UD (20/08/2025, 1 h)</t>
         </is>
       </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Sebastian Camilo Vanegas Ayala – 2025.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
@@ -1688,332 +1751,25 @@
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="6" t="n"/>
       <c r="J35" s="6" t="n"/>
+      <c r="K35" s="6" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:J35"/>
+  <autoFilter ref="A4:K35"/>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Capacitaciones con certificado reportadas por los profesores</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Certificados recientes entregados por los profesores; los documentos se resguardan en el archivo del programa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Profesor</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Capacitación</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Entidad</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Horas</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Año</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>Soporte</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Gomez Vargas Ernesto</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Taller de formación EUR-ACE «Aseguramiento de calidad y acreditación internacional EUR-ACE de programas educativos en ingeniería»</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>ENAEE, ENTEA y LACCEI (Girardot, Colombia)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>08/11/2022 al 10/11/2022</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>2022</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Certificado en archivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Ortiz Davila Alvaro Enrique</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Introduction to GeoWebApp Building with open-source tools (curso en línea)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Universidad de Twente (ITC) y Geoversity</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>13/05/2024</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>2024</v>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Certificado en archivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Ortiz Davila Alvaro Enrique</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Curso Internacional de Competencias Docentes y Diseño de Materiales Didácticos para la Educación en Línea (título propio, calificación 9,60)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Universidad Internacional de La Rioja (UNIR)</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>04/05/2026 al 05/07/2026</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>125</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>2026</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Certificado en archivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Plazas Nossa Leonardo</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Data Science and Machine Learning: Making Data-Driven Decisions</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>MIT Schwarzman College of Computing y MIT IDSS</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>agosto de 2023</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>2023</v>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Certificado en archivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Vanegas Ayala Sebastian Camilo</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Taller «Instalación local de modelos de IA»</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Vicerrectoría Académica y Comité PlanEsTIC-UD</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>16/07/2025</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Certificado en archivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Vanegas Ayala Sebastian Camilo</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Taller «Automatización de tareas de ofimática con IA a través del uso de protocolo MCP»</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Vicerrectoría Académica y Comité PlanEsTIC-UD</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>15/07/2025</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>Certificado en archivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Vanegas Ayala Sebastian Camilo</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Taller «Da vida a tus ideas con presentaciones creativas e impactantes en Gamma AI»</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Vicerrectoría Académica y Comité PlanEsTIC-UD</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>20/08/2025</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Certificado en archivo</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:G11"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2125,10 +1881,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="15" t="n">
         <v>45889</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="15" t="n">
         <v>45891</v>
       </c>
       <c r="I5" s="6" t="n">
@@ -2166,10 +1922,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="16" t="n">
         <v>45855</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="16" t="n">
         <v>45864</v>
       </c>
       <c r="I6" s="12" t="n">
@@ -2207,10 +1963,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="15" t="n">
         <v>45852</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="15" t="n">
         <v>45863</v>
       </c>
       <c r="I7" s="6" t="n">
@@ -2248,10 +2004,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="16" t="n">
         <v>45839</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="16" t="n">
         <v>45841</v>
       </c>
       <c r="I8" s="12" t="n">
@@ -2289,10 +2045,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="15" t="n">
         <v>45722</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="15" t="n">
         <v>45724</v>
       </c>
       <c r="I9" s="6" t="n">
@@ -2330,10 +2086,10 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="16" t="n">
         <v>45712</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="16" t="n">
         <v>45716</v>
       </c>
       <c r="I10" s="12" t="n">
@@ -2371,10 +2127,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="15" t="n">
         <v>45712</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="15" t="n">
         <v>45723</v>
       </c>
       <c r="I11" s="6" t="n">
@@ -2412,10 +2168,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="16" t="n">
         <v>45600</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="16" t="n">
         <v>45604</v>
       </c>
       <c r="I12" s="12" t="n">
@@ -2453,10 +2209,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="15" t="n">
         <v>45600</v>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="15" t="n">
         <v>45604</v>
       </c>
       <c r="I13" s="6" t="n">
@@ -2494,10 +2250,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="16" t="n">
         <v>45588</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="16" t="n">
         <v>45590</v>
       </c>
       <c r="I14" s="12" t="n">
@@ -2535,10 +2291,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="15" t="n">
         <v>45581</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="15" t="n">
         <v>45583</v>
       </c>
       <c r="I15" s="6" t="n">
@@ -2576,10 +2332,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G16" s="16" t="n">
         <v>45580</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="H16" s="16" t="n">
         <v>45591</v>
       </c>
       <c r="I16" s="12" t="n">
@@ -2617,10 +2373,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="15" t="n">
         <v>45559</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="15" t="n">
         <v>45562</v>
       </c>
       <c r="I17" s="6" t="n">
@@ -2658,10 +2414,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G18" s="14" t="n">
+      <c r="G18" s="16" t="n">
         <v>45486</v>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="H18" s="16" t="n">
         <v>45489</v>
       </c>
       <c r="I18" s="12" t="n">
@@ -2699,10 +2455,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="15" t="n">
         <v>45481</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="15" t="n">
         <v>45492</v>
       </c>
       <c r="I19" s="6" t="n">
@@ -2740,10 +2496,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G20" s="14" t="n">
+      <c r="G20" s="16" t="n">
         <v>45468</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H20" s="16" t="n">
         <v>45471</v>
       </c>
       <c r="I20" s="12" t="n">
@@ -2781,10 +2537,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="15" t="n">
         <v>45447</v>
       </c>
-      <c r="H21" s="13" t="n">
+      <c r="H21" s="15" t="n">
         <v>45450</v>
       </c>
       <c r="I21" s="6" t="n">
@@ -2822,10 +2578,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G22" s="14" t="n">
+      <c r="G22" s="16" t="n">
         <v>45431</v>
       </c>
-      <c r="H22" s="14" t="n">
+      <c r="H22" s="16" t="n">
         <v>45436</v>
       </c>
       <c r="I22" s="12" t="n">
@@ -2863,10 +2619,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="15" t="n">
         <v>45383</v>
       </c>
-      <c r="H23" s="13" t="n">
+      <c r="H23" s="15" t="n">
         <v>45387</v>
       </c>
       <c r="I23" s="6" t="n">
@@ -2904,10 +2660,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G24" s="14" t="n">
+      <c r="G24" s="16" t="n">
         <v>45257</v>
       </c>
-      <c r="H24" s="14" t="n">
+      <c r="H24" s="16" t="n">
         <v>45257</v>
       </c>
       <c r="I24" s="12" t="n">
@@ -2945,10 +2701,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="15" t="n">
         <v>45253</v>
       </c>
-      <c r="H25" s="13" t="n">
+      <c r="H25" s="15" t="n">
         <v>45254</v>
       </c>
       <c r="I25" s="6" t="n">
@@ -2986,10 +2742,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G26" s="14" t="n">
+      <c r="G26" s="16" t="n">
         <v>45253</v>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="H26" s="16" t="n">
         <v>45254</v>
       </c>
       <c r="I26" s="12" t="n">
@@ -3027,10 +2783,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="15" t="n">
         <v>45253</v>
       </c>
-      <c r="H27" s="13" t="n">
+      <c r="H27" s="15" t="n">
         <v>45254</v>
       </c>
       <c r="I27" s="6" t="n">
@@ -3068,10 +2824,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G28" s="14" t="n">
+      <c r="G28" s="16" t="n">
         <v>45253</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H28" s="16" t="n">
         <v>45254</v>
       </c>
       <c r="I28" s="12" t="n">
@@ -3109,10 +2865,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="15" t="n">
         <v>45253</v>
       </c>
-      <c r="H29" s="13" t="n">
+      <c r="H29" s="15" t="n">
         <v>45254</v>
       </c>
       <c r="I29" s="6" t="n">
@@ -3150,10 +2906,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G30" s="14" t="n">
+      <c r="G30" s="16" t="n">
         <v>45250</v>
       </c>
-      <c r="H30" s="14" t="n">
+      <c r="H30" s="16" t="n">
         <v>45254</v>
       </c>
       <c r="I30" s="12" t="n">
@@ -3191,10 +2947,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="15" t="n">
         <v>45237</v>
       </c>
-      <c r="H31" s="13" t="n">
+      <c r="H31" s="15" t="n">
         <v>45240</v>
       </c>
       <c r="I31" s="6" t="n">
@@ -3232,10 +2988,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G32" s="14" t="n">
+      <c r="G32" s="16" t="n">
         <v>45237</v>
       </c>
-      <c r="H32" s="14" t="n">
+      <c r="H32" s="16" t="n">
         <v>45240</v>
       </c>
       <c r="I32" s="12" t="n">
@@ -3273,10 +3029,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="15" t="n">
         <v>45237</v>
       </c>
-      <c r="H33" s="13" t="n">
+      <c r="H33" s="15" t="n">
         <v>45247</v>
       </c>
       <c r="I33" s="6" t="n">
@@ -3314,10 +3070,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G34" s="14" t="n">
+      <c r="G34" s="16" t="n">
         <v>45232</v>
       </c>
-      <c r="H34" s="14" t="n">
+      <c r="H34" s="16" t="n">
         <v>45234</v>
       </c>
       <c r="I34" s="12" t="n">
@@ -3355,10 +3111,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="G35" s="15" t="n">
         <v>45224</v>
       </c>
-      <c r="H35" s="13" t="n">
+      <c r="H35" s="15" t="n">
         <v>45226</v>
       </c>
       <c r="I35" s="6" t="n">
@@ -3396,10 +3152,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G36" s="14" t="n">
+      <c r="G36" s="16" t="n">
         <v>45216</v>
       </c>
-      <c r="H36" s="14" t="n">
+      <c r="H36" s="16" t="n">
         <v>45219</v>
       </c>
       <c r="I36" s="12" t="n">
@@ -3437,10 +3193,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="15" t="n">
         <v>45188</v>
       </c>
-      <c r="H37" s="13" t="n">
+      <c r="H37" s="15" t="n">
         <v>45191</v>
       </c>
       <c r="I37" s="6" t="n">
@@ -3478,10 +3234,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G38" s="14" t="n">
+      <c r="G38" s="16" t="n">
         <v>45181</v>
       </c>
-      <c r="H38" s="14" t="n">
+      <c r="H38" s="16" t="n">
         <v>45184</v>
       </c>
       <c r="I38" s="12" t="n">
@@ -3519,10 +3275,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="G39" s="15" t="n">
         <v>45126</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="H39" s="15" t="n">
         <v>45128</v>
       </c>
       <c r="I39" s="6" t="n">
@@ -3560,10 +3316,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G40" s="14" t="n">
+      <c r="G40" s="16" t="n">
         <v>45124</v>
       </c>
-      <c r="H40" s="14" t="n">
+      <c r="H40" s="16" t="n">
         <v>45128</v>
       </c>
       <c r="I40" s="12" t="n">
@@ -3601,10 +3357,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="15" t="n">
         <v>45074</v>
       </c>
-      <c r="H41" s="13" t="n">
+      <c r="H41" s="15" t="n">
         <v>45078</v>
       </c>
       <c r="I41" s="6" t="n">
@@ -3642,10 +3398,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G42" s="14" t="n">
+      <c r="G42" s="16" t="n">
         <v>45050</v>
       </c>
-      <c r="H42" s="14" t="n">
+      <c r="H42" s="16" t="n">
         <v>45052</v>
       </c>
       <c r="I42" s="12" t="n">
@@ -3683,10 +3439,10 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="G43" s="15" t="n">
         <v>45048</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="H43" s="15" t="n">
         <v>45138</v>
       </c>
       <c r="I43" s="6" t="n">
@@ -3724,10 +3480,10 @@
           <t>Presencial</t>
         </is>
       </c>
-      <c r="G44" s="14" t="n">
+      <c r="G44" s="16" t="n">
         <v>45038</v>
       </c>
-      <c r="H44" s="14" t="n">
+      <c r="H44" s="16" t="n">
         <v>45042</v>
       </c>
       <c r="I44" s="12" t="n">
@@ -3765,10 +3521,10 @@
           <t>Virtual</t>
         </is>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="G45" s="15" t="n">
         <v>44620</v>
       </c>
-      <c r="H45" s="13" t="n">
+      <c r="H45" s="15" t="n">
         <v>44681</v>
       </c>
       <c r="I45" s="6" t="n">

--- a/NuevaData/Presentacion/Investigacion/FACTOR 3. PROFESORES/a. Informes de participación de los docentes/F3_Participacion_Docente_Capacitacion.xlsx
+++ b/NuevaData/Presentacion/Investigacion/FACTOR 3. PROFESORES/a. Informes de participación de los docentes/F3_Participacion_Docente_Capacitacion.xlsx
@@ -717,10 +717,10 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" ht="39" customHeight="1">
+    <row r="13" ht="65" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>La planta docente es común a las dos modalidades: el Cuadro Maestro CNA No. 05 de SNIES 17528 (Investigación) y el de SNIES 116070 (Profundización) relacionan los mismos profesores. Por eso este libro es el mismo en las carpetas de Investigación y de Profundización. Grupo y categoría de investigador: Cuadro Maestro CNA No. 05.</t>
+          <t>Este libro es el único listado de profesores del factor: los de la Decanatura que participan en la Maestría. La planta docente es común a las dos modalidades, por eso es el mismo en las carpetas de Investigación y de Profundización y el porcentaje es el mismo para ambas. El listado de la Decanatura relaciona más profesores; se retiraron los que no hacen parte de la Maestría y se agregó el profesor que reportó su certificado. Grupo y categoría de investigador: Cuadro Maestro CNA No. 05.</t>
         </is>
       </c>
     </row>
